--- a/wellanders/retriever/behöva_0.5.xlsx
+++ b/wellanders/retriever/behöva_0.5.xlsx
@@ -1,42 +1,1157 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\DGU\Repos\Cassandra\wellanders\retriever\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_F5628729C261802C1C43100E80872164B10B72BF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>"behöver vara" OR "behöver göra" OR "behöver få" OR "behöver ha" OR "behöver ta" OR "behöver bli" OR "behöver gå" OR "behöver komma" OR "behöver veta" OR "behöver se" OR "behöver betala" OR "behöver jobba" OR "behöver öka" OR "behöver tänka" OR "behöver kunna" OR "behöver bygga" OR "behöver prata" OR "behöver lära" OR "behöver vila" OR "behöver hitta" OR "behöver oroa" OR "behöver känna" OR "behöver spara" OR "behöver använda"</t>
+  </si>
+  <si>
+    <t>"behöver att få" OR "behöver att skriva" OR "behöver att göra" OR "behöver att ta" OR "behöver att ha" OR "behöver att kunna" OR "behöver att bryta"</t>
+  </si>
+  <si>
+    <t>1945</t>
+  </si>
+  <si>
+    <t>1946</t>
+  </si>
+  <si>
+    <t>1947</t>
+  </si>
+  <si>
+    <t>1948</t>
+  </si>
+  <si>
+    <t>1949</t>
+  </si>
+  <si>
+    <t>1950</t>
+  </si>
+  <si>
+    <t>1951</t>
+  </si>
+  <si>
+    <t>1952</t>
+  </si>
+  <si>
+    <t>1953</t>
+  </si>
+  <si>
+    <t>1954</t>
+  </si>
+  <si>
+    <t>1955</t>
+  </si>
+  <si>
+    <t>1956</t>
+  </si>
+  <si>
+    <t>1957</t>
+  </si>
+  <si>
+    <t>1958</t>
+  </si>
+  <si>
+    <t>1959</t>
+  </si>
+  <si>
+    <t>1960</t>
+  </si>
+  <si>
+    <t>1961</t>
+  </si>
+  <si>
+    <t>1962</t>
+  </si>
+  <si>
+    <t>1963</t>
+  </si>
+  <si>
+    <t>1964</t>
+  </si>
+  <si>
+    <t>1965</t>
+  </si>
+  <si>
+    <t>1966</t>
+  </si>
+  <si>
+    <t>1967</t>
+  </si>
+  <si>
+    <t>1968</t>
+  </si>
+  <si>
+    <t>1969</t>
+  </si>
+  <si>
+    <t>1970</t>
+  </si>
+  <si>
+    <t>1971</t>
+  </si>
+  <si>
+    <t>1972</t>
+  </si>
+  <si>
+    <t>1973</t>
+  </si>
+  <si>
+    <t>1974</t>
+  </si>
+  <si>
+    <t>1975</t>
+  </si>
+  <si>
+    <t>1976</t>
+  </si>
+  <si>
+    <t>1977</t>
+  </si>
+  <si>
+    <t>1978</t>
+  </si>
+  <si>
+    <t>1979</t>
+  </si>
+  <si>
+    <t>1980</t>
+  </si>
+  <si>
+    <t>1981</t>
+  </si>
+  <si>
+    <t>1982</t>
+  </si>
+  <si>
+    <t>1983</t>
+  </si>
+  <si>
+    <t>1984</t>
+  </si>
+  <si>
+    <t>1985</t>
+  </si>
+  <si>
+    <t>1986</t>
+  </si>
+  <si>
+    <t>1987</t>
+  </si>
+  <si>
+    <t>1988</t>
+  </si>
+  <si>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>1990</t>
+  </si>
+  <si>
+    <t>1991</t>
+  </si>
+  <si>
+    <t>1992</t>
+  </si>
+  <si>
+    <t>1993</t>
+  </si>
+  <si>
+    <t>1994</t>
+  </si>
+  <si>
+    <t>1995</t>
+  </si>
+  <si>
+    <t>1996</t>
+  </si>
+  <si>
+    <t>1997</t>
+  </si>
+  <si>
+    <t>1998</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+</sst>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C83"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>"behöver vara" OR "behöver göra" OR "behöver få" OR "behöver ha" OR "behöver ta" OR "behöver bli" OR "behöver gå" OR "behöver komma" OR "behöver veta" OR "behöver se" OR "behöver betala" OR "behöver jobba" OR "behöver öka" OR "behöver tänka" OR "behöver kunna" OR "behöver bygga" OR "behöver prata" OR "behöver lära" OR "behöver vila" OR "behöver hitta" OR "behöver oroa" OR "behöver känna" OR "behöver spara" OR "behöver använda"
-</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>"behöver att få" OR "behöver att skriva" OR "behöver att göra" OR "behöver att ta" OR "behöver att ha" OR "behöver att kunna" OR "behöver att bryta"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -45,11 +1160,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -58,11 +1171,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -71,11 +1182,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -84,11 +1193,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -97,11 +1204,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -110,11 +1215,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -123,11 +1226,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -136,11 +1237,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -149,11 +1248,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -162,11 +1259,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -175,11 +1270,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -188,11 +1281,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -201,11 +1292,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -214,11 +1303,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -227,11 +1314,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>18</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -240,11 +1325,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -253,11 +1336,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -266,11 +1347,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -279,11 +1358,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>22</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -292,11 +1369,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>23</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -305,11 +1380,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>24</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -318,11 +1391,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>25</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -331,11 +1402,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>26</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -344,11 +1413,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>27</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -357,11 +1424,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>28</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -370,11 +1435,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>29</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -383,11 +1446,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -396,11 +1457,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>31</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -409,11 +1468,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>32</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -422,11 +1479,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>33</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -435,11 +1490,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>34</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -448,11 +1501,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>35</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -461,11 +1512,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -474,11 +1523,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -487,11 +1534,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>38</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -500,11 +1545,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>39</v>
       </c>
       <c r="B38">
         <v>32</v>
@@ -513,11 +1556,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>40</v>
       </c>
       <c r="B39">
         <v>138</v>
@@ -526,11 +1567,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
       </c>
       <c r="B40">
         <v>128</v>
@@ -539,11 +1578,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>42</v>
       </c>
       <c r="B41">
         <v>128</v>
@@ -552,11 +1589,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>43</v>
       </c>
       <c r="B42">
         <v>182</v>
@@ -565,11 +1600,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>44</v>
       </c>
       <c r="B43">
         <v>189</v>
@@ -578,11 +1611,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>45</v>
       </c>
       <c r="B44">
         <v>170</v>
@@ -591,11 +1622,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>46</v>
       </c>
       <c r="B45">
         <v>199</v>
@@ -604,11 +1633,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>47</v>
       </c>
       <c r="B46">
         <v>236</v>
@@ -617,11 +1644,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>48</v>
       </c>
       <c r="B47">
         <v>424</v>
@@ -630,11 +1655,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>49</v>
       </c>
       <c r="B48">
         <v>442</v>
@@ -643,11 +1666,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>50</v>
       </c>
       <c r="B49">
         <v>600</v>
@@ -656,11 +1677,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>51</v>
       </c>
       <c r="B50">
         <v>730</v>
@@ -669,11 +1688,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>52</v>
       </c>
       <c r="B51">
         <v>1198</v>
@@ -682,11 +1699,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>53</v>
       </c>
       <c r="B52">
         <v>2379</v>
@@ -695,11 +1710,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>54</v>
       </c>
       <c r="B53">
         <v>2557</v>
@@ -708,11 +1721,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>55</v>
       </c>
       <c r="B54">
         <v>2790</v>
@@ -721,11 +1732,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>56</v>
       </c>
       <c r="B55">
         <v>3164</v>
@@ -734,11 +1743,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>57</v>
       </c>
       <c r="B56">
         <v>4178</v>
@@ -747,11 +1754,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>58</v>
       </c>
       <c r="B57">
         <v>5126</v>
@@ -760,11 +1765,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>59</v>
       </c>
       <c r="B58">
         <v>7193</v>
@@ -773,11 +1776,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>60</v>
       </c>
       <c r="B59">
         <v>16995</v>
@@ -786,11 +1787,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>61</v>
       </c>
       <c r="B60">
         <v>17769</v>
@@ -799,11 +1798,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>62</v>
       </c>
       <c r="B61">
         <v>22165</v>
@@ -812,11 +1809,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>63</v>
       </c>
       <c r="B62">
         <v>25081</v>
@@ -825,11 +1820,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>64</v>
       </c>
       <c r="B63">
         <v>27095</v>
@@ -838,11 +1831,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>65</v>
       </c>
       <c r="B64">
         <v>34778</v>
@@ -851,11 +1842,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>66</v>
       </c>
       <c r="B65">
         <v>46323</v>
@@ -864,11 +1853,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>67</v>
       </c>
       <c r="B66">
         <v>53228</v>
@@ -877,11 +1864,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>68</v>
       </c>
       <c r="B67">
         <v>82980</v>
@@ -890,11 +1875,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>69</v>
       </c>
       <c r="B68">
         <v>68583</v>
@@ -903,11 +1886,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>70</v>
       </c>
       <c r="B69">
         <v>62540</v>
@@ -916,11 +1897,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>71</v>
       </c>
       <c r="B70">
         <v>71737</v>
@@ -929,11 +1908,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>72</v>
       </c>
       <c r="B71">
         <v>84809</v>
@@ -942,11 +1919,9 @@
         <v>146</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>73</v>
       </c>
       <c r="B72">
         <v>90949</v>
@@ -955,11 +1930,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>74</v>
       </c>
       <c r="B73">
         <v>109679</v>
@@ -968,11 +1941,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>75</v>
       </c>
       <c r="B74">
         <v>120509</v>
@@ -981,11 +1952,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>76</v>
       </c>
       <c r="B75">
         <v>134939</v>
@@ -994,11 +1963,9 @@
         <v>123</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>77</v>
       </c>
       <c r="B76">
         <v>149895</v>
@@ -1007,11 +1974,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>78</v>
       </c>
       <c r="B77">
         <v>160101</v>
@@ -1020,11 +1985,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>79</v>
       </c>
       <c r="B78">
         <v>165895</v>
@@ -1033,11 +1996,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>80</v>
       </c>
       <c r="B79">
         <v>173952</v>
@@ -1046,11 +2007,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>81</v>
       </c>
       <c r="B80">
         <v>172980</v>
@@ -1059,11 +2018,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>82</v>
       </c>
       <c r="B81">
         <v>141313</v>
@@ -1072,11 +2029,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>83</v>
       </c>
       <c r="B82">
         <v>144856</v>
@@ -1085,11 +2040,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>84</v>
       </c>
       <c r="B83">
         <v>79141</v>
@@ -1099,5 +2052,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>